--- a/Design-Files/WIFI_BoardV4.0/BOM/Client-BOM-WIFI_BoardV4.00.xlsx
+++ b/Design-Files/WIFI_BoardV4.0/BOM/Client-BOM-WIFI_BoardV4.00.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="247">
   <si>
     <t>#</t>
   </si>
@@ -138,9 +138,6 @@
     <t>D3</t>
   </si>
   <si>
-    <t>D4, D5, D6, D7, D8, D9</t>
-  </si>
-  <si>
     <t>D10</t>
   </si>
   <si>
@@ -369,9 +366,6 @@
     <t>SWITCH TACTILE SPST-NO 0.05A 12V</t>
   </si>
   <si>
-    <t>ROTARY ENCODER MECHANICAL 24PPR</t>
-  </si>
-  <si>
     <t>SMD,18x25.5mm WiFi Modules ROHS</t>
   </si>
   <si>
@@ -441,9 +435,6 @@
     <t>B3U-1000P</t>
   </si>
   <si>
-    <t>PEC11R-4215F-N0024</t>
-  </si>
-  <si>
     <t>AS312</t>
   </si>
   <si>
@@ -754,6 +745,21 @@
   </si>
   <si>
     <t>EYA DISPLAY</t>
+  </si>
+  <si>
+    <t>R32</t>
+  </si>
+  <si>
+    <t>DNP</t>
+  </si>
+  <si>
+    <t>ENCODER MECH QUAD VERT PC PIN</t>
+  </si>
+  <si>
+    <t>PEC11R-4215F-S0024</t>
+  </si>
+  <si>
+    <t>D4, D5, D6, D7, D8, D9, D11, D12, D13</t>
   </si>
 </sst>
 </file>
@@ -934,7 +940,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -980,10 +986,13 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1274,7 +1283,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
@@ -1298,9 +1307,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1314,25 +1323,25 @@
         <v>24</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1348,19 +1357,19 @@
         <v>25</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J3" s="6">
         <v>2</v>
@@ -1370,7 +1379,7 @@
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="10">
-        <f t="shared" ref="B4:B51" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B52" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
@@ -1380,19 +1389,19 @@
         <v>26</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="J4" s="8">
         <v>1</v>
@@ -1412,19 +1421,19 @@
         <v>27</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J5" s="6">
         <v>4</v>
@@ -1444,19 +1453,19 @@
         <v>28</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J6" s="8">
         <v>1</v>
@@ -1476,19 +1485,19 @@
         <v>29</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="J7" s="6">
         <v>1</v>
@@ -1508,19 +1517,19 @@
         <v>30</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J8" s="8">
         <v>1</v>
@@ -1540,19 +1549,19 @@
         <v>31</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J9" s="6">
         <v>2</v>
@@ -1572,19 +1581,19 @@
         <v>32</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="J10" s="8">
         <v>1</v>
@@ -1604,19 +1613,19 @@
         <v>33</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J11" s="6">
         <v>1</v>
@@ -1636,19 +1645,19 @@
         <v>34</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J12" s="8">
         <v>1</v>
@@ -1668,19 +1677,19 @@
         <v>35</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J13" s="6">
         <v>1</v>
@@ -1700,19 +1709,19 @@
         <v>36</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J14" s="8">
         <v>1</v>
@@ -1732,19 +1741,19 @@
         <v>37</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J15" s="6">
         <v>1</v>
@@ -1764,19 +1773,19 @@
         <v>38</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J16" s="8">
         <v>1</v>
@@ -1793,25 +1802,25 @@
         <v>5</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>39</v>
+        <v>246</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J17" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K17" s="6"/>
     </row>
@@ -1825,22 +1834,22 @@
         <v>4</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J18" s="8">
         <v>1</v>
@@ -1857,22 +1866,22 @@
         <v>6</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J19" s="6">
         <v>1</v>
@@ -1889,22 +1898,22 @@
         <v>7</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J20" s="8">
         <v>1</v>
@@ -1921,22 +1930,22 @@
         <v>8</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J21" s="6">
         <v>1</v>
@@ -1953,22 +1962,22 @@
         <v>9</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J22" s="8">
         <v>1</v>
@@ -1985,22 +1994,22 @@
         <v>10</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J23" s="6">
         <v>1</v>
@@ -2017,22 +2026,22 @@
         <v>11</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J24" s="8">
         <v>1</v>
@@ -2049,28 +2058,28 @@
         <v>12</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J25" s="13">
         <v>5</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2083,22 +2092,22 @@
         <v>13</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J26" s="8">
         <v>1</v>
@@ -2115,22 +2124,22 @@
         <v>13</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J27" s="6">
         <v>2</v>
@@ -2147,22 +2156,22 @@
         <v>14</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J28" s="8">
         <v>1</v>
@@ -2179,22 +2188,22 @@
         <v>15</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="J29" s="6">
         <v>4</v>
@@ -2211,22 +2220,22 @@
         <v>15</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="J30" s="8">
         <v>3</v>
@@ -2243,22 +2252,22 @@
         <v>15</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="J31" s="6">
         <v>2</v>
@@ -2275,22 +2284,22 @@
         <v>15</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="J32" s="8">
         <v>2</v>
@@ -2307,22 +2316,22 @@
         <v>15</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="J33" s="6">
         <v>4</v>
@@ -2339,22 +2348,22 @@
         <v>15</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="J34" s="8">
         <v>1</v>
@@ -2371,22 +2380,22 @@
         <v>15</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="J35" s="6">
         <v>1</v>
@@ -2403,22 +2412,22 @@
         <v>16</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="J36" s="8">
         <v>1</v>
@@ -2435,22 +2444,22 @@
         <v>15</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J37" s="6">
         <v>2</v>
@@ -2467,22 +2476,22 @@
         <v>15</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J38" s="8">
         <v>2</v>
@@ -2499,22 +2508,22 @@
         <v>16</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="J39" s="6">
         <v>2</v>
@@ -2531,22 +2540,22 @@
         <v>15</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J40" s="8">
         <v>1</v>
@@ -2563,22 +2572,22 @@
         <v>15</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J41" s="6">
         <v>1</v>
@@ -2595,22 +2604,22 @@
         <v>15</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="J42" s="8">
         <v>2</v>
@@ -2627,22 +2636,22 @@
         <v>15</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="J43" s="6">
         <v>1</v>
@@ -2652,256 +2661,289 @@
     <row r="44" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B44" si="1">ROW(B44) - ROW($B$2)</f>
         <v>42</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="J44" s="8">
-        <v>2</v>
-      </c>
-      <c r="K44" s="8"/>
+        <v>15</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="G44" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="H44" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="I44" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="J44" s="19">
+        <v>1</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="45" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="10">
-        <f>ROW(B45) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C45" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>116</v>
+      <c r="C45" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>114</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>207</v>
+        <v>237</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>203</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="J45" s="6">
-        <v>1</v>
-      </c>
-      <c r="K45" s="6"/>
+        <v>235</v>
+      </c>
+      <c r="J45" s="8">
+        <v>2</v>
+      </c>
+      <c r="K45" s="8"/>
     </row>
     <row r="46" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="10">
-        <f t="shared" si="0"/>
+        <f>ROW(B46) - ROW($B$2)</f>
         <v>44</v>
       </c>
-      <c r="C46" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>68</v>
+      <c r="C46" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>240</v>
+        <v>244</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>245</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>182</v>
+        <v>245</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J46" s="8">
-        <v>3</v>
-      </c>
-      <c r="K46" s="8"/>
+        <v>1</v>
+      </c>
+      <c r="K46" s="6"/>
     </row>
     <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="10">
-        <f>ROW(B47) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C47" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>117</v>
+      <c r="C47" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>114</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>209</v>
+        <v>237</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>205</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="J47" s="6">
-        <v>1</v>
-      </c>
-      <c r="K47" s="6"/>
-    </row>
-    <row r="48" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+      <c r="J47" s="8">
+        <v>3</v>
+      </c>
+      <c r="K47" s="8"/>
+    </row>
+    <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="10">
-        <f t="shared" si="0"/>
+        <f>ROW(B48) - ROW($B$2)</f>
         <v>46</v>
       </c>
-      <c r="C48" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>118</v>
+      <c r="C48" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>210</v>
+        <v>237</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="J48" s="8">
-        <v>1</v>
-      </c>
-      <c r="K48" s="8"/>
-    </row>
-    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+      <c r="J48" s="6">
+        <v>1</v>
+      </c>
+      <c r="K48" s="6"/>
+    </row>
+    <row r="49" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="10">
-        <f>ROW(B49) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C49" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>119</v>
+      <c r="C49" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>211</v>
+        <v>237</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>207</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="J49" s="6">
-        <v>1</v>
-      </c>
-      <c r="K49" s="6"/>
-    </row>
-    <row r="50" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+      <c r="J49" s="8">
+        <v>1</v>
+      </c>
+      <c r="K49" s="8"/>
+    </row>
+    <row r="50" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="10">
-        <f t="shared" si="0"/>
+        <f>ROW(B50) - ROW($B$2)</f>
         <v>48</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="H50" s="8" t="s">
-        <v>212</v>
+      <c r="C50" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>208</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="J50" s="8">
-        <v>1</v>
-      </c>
-      <c r="K50" s="8"/>
-    </row>
-    <row r="51" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+      <c r="J50" s="6">
+        <v>1</v>
+      </c>
+      <c r="K50" s="6"/>
+    </row>
+    <row r="51" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="10">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="C51" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J51" s="8">
+        <v>1</v>
+      </c>
+      <c r="K51" s="8"/>
+    </row>
+    <row r="52" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="10">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="E52" s="9"/>
+      <c r="F52" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H52" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="D51" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="E51" s="9"/>
-      <c r="F51" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="H51" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="I51" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="J51" s="8">
-        <v>1</v>
-      </c>
-      <c r="K51" s="18" t="s">
-        <v>242</v>
+      <c r="I52" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="J52" s="8">
+        <v>1</v>
+      </c>
+      <c r="K52" s="17" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -2909,7 +2951,7 @@
     <mergeCell ref="I1:K1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="K51" r:id="rId1"/>
+    <hyperlink ref="K52" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
